--- a/Result/profitability/3380.xlsx
+++ b/Result/profitability/3380.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.29</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.02125000000000002</v>
+        <v>-0.01375000000000002</v>
       </c>
       <c r="N2" t="n">
-        <v>17.98</v>
+        <v>17.75625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.77</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08124999999999999</v>
+        <v>0.10125</v>
       </c>
       <c r="N3" t="n">
-        <v>17.78125</v>
+        <v>17.70625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.13</v>
       </c>
       <c r="M4" t="n">
-        <v>0.24125</v>
+        <v>0.2675</v>
       </c>
       <c r="N4" t="n">
-        <v>17.595</v>
+        <v>17.51625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.23</v>
       </c>
       <c r="M5" t="n">
-        <v>0.295</v>
+        <v>0.32</v>
       </c>
       <c r="N5" t="n">
-        <v>17.72625</v>
+        <v>18.035</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.47</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3774999999999999</v>
+        <v>0.37625</v>
       </c>
       <c r="N6" t="n">
-        <v>18.81</v>
+        <v>18.8475</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1267,7 +1267,7 @@
         <v>0.395</v>
       </c>
       <c r="N7" t="n">
-        <v>18.835</v>
+        <v>18.745</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.5</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4562499999999999</v>
+        <v>0.445</v>
       </c>
       <c r="N8" t="n">
-        <v>18.83625</v>
+        <v>18.75625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5299999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="N9" t="n">
         <v>18.9175</v>
@@ -1645,7 +1645,7 @@
         <v>0.33</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5349999999999999</v>
+        <v>0.535</v>
       </c>
       <c r="N10" t="n">
         <v>18.71</v>
@@ -1899,7 +1899,7 @@
         <v>0.72</v>
       </c>
       <c r="M12" t="n">
-        <v>0.47375</v>
+        <v>0.4737499999999999</v>
       </c>
       <c r="N12" t="n">
         <v>18.215</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3380</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5166</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4250</v>
+      </c>
+      <c r="E75" t="n">
+        <v>915</v>
+      </c>
+      <c r="F75" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-66</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-1.27%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>53</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="K75" t="n">
+        <v>8</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.05625000000000002</v>
+      </c>
+      <c r="N75" t="n">
+        <v>17.92125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.09000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.6400000000000006</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03485838779956429</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.052631578947368</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.469999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.161967213114754</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
